--- a/docs/reports/內在價值報告_20261016.xlsx
+++ b/docs/reports/內在價值報告_20261016.xlsx
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>521.963</v>
+        <v>531.877</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>345.79</v>
+        <v>346.2</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6405,7 +6405,7 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>603.4</v>
+        <v>604.2</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>355.5</v>
+        <v>344.1</v>
       </c>
       <c r="E52" s="23" t="inlineStr"/>
       <c r="F52" s="22" t="inlineStr">
@@ -6889,7 +6889,7 @@
         <v>15.3128</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>465.6</v>
+        <v>447.4</v>
       </c>
       <c r="M52" s="25" t="n">
         <v>25</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AE52" s="22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AF52" s="23" t="inlineStr">
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>546.715</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="E54" s="23" t="inlineStr"/>
       <c r="F54" s="22" t="inlineStr">
@@ -7127,13 +7127,13 @@
         <v>81.6728</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>3.4472</v>
+        <v>3.4474</v>
       </c>
       <c r="K54" s="24" t="n">
         <v>86.59699999999999</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>569.4</v>
+        <v>551.5</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AE54" s="22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AF54" s="23" t="inlineStr">
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>345.79</v>
+        <v>346.2</v>
       </c>
       <c r="D52" s="34" t="n">
         <v>49.1601</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>521.963</v>
+        <v>531.877</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="L54" s="34" t="inlineStr"/>
       <c r="M54" s="34" t="n">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
       <c r="N54" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>355.5</v>
+        <v>344.1</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>546.715</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6728</v>
@@ -12729,7 +12729,7 @@
       <c r="G61" s="34" t="inlineStr"/>
       <c r="H61" s="34" t="inlineStr"/>
       <c r="I61" s="34" t="n">
-        <v>3.4472</v>
+        <v>3.4474</v>
       </c>
       <c r="J61" s="34" t="n">
         <v>3.3891</v>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>345.79</v>
+        <v>346.2</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>7.034</v>
+        <v>7.0423</v>
       </c>
       <c r="L52" s="24" t="n">
         <v>36.8701</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>521.963</v>
+        <v>531.877</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>355.5</v>
+        <v>344.1</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.6558</v>
+        <v>5.4744</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -16052,7 +16052,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>546.715</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.694</v>
+        <v>6.5145</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2546</v>
@@ -21453,7 +21453,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>345.79</v>
+        <v>346.2</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21627,7 +21627,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>521.963</v>
+        <v>531.877</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21871,7 +21871,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>355.5</v>
+        <v>344.1</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>546.715</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>345.79</v>
+        <v>346.2</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26354,7 +26354,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>521.963</v>
+        <v>531.877</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5</v>
@@ -26537,7 +26537,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>355.5</v>
+        <v>344.1</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.5</v>
@@ -26781,7 +26781,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>546.715</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.5</v>
